--- a/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636794039</v>
+        <v>10.8449762099728</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907206639359</v>
+        <v>37.78907151595916</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.96175289726338</v>
+        <v>6.608143797285281</v>
       </c>
       <c r="C2" t="n">
-        <v>4.310854169347744</v>
+        <v>7.567311304334415</v>
       </c>
       <c r="D2" t="n">
-        <v>32.27397402940964</v>
+        <v>27.52820562708056</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56699250916493</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="C3" t="n">
-        <v>25.07874510498477</v>
+        <v>19.25698121880119</v>
       </c>
       <c r="D3" t="n">
-        <v>83.51236846175493</v>
+        <v>83.0902169489288</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.91880234465055</v>
+        <v>32.78742807873073</v>
       </c>
       <c r="C4" t="n">
-        <v>56.43674852633215</v>
+        <v>50.25959197121121</v>
       </c>
       <c r="D4" t="n">
-        <v>88.27973531357743</v>
+        <v>115.9365498899143</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.80419990516094</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="C5" t="n">
-        <v>95.74494485667019</v>
+        <v>100.4082464518426</v>
       </c>
       <c r="D5" t="n">
-        <v>59.76389149602459</v>
+        <v>79.03069019186825</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>43.83405324691584</v>
       </c>
       <c r="C6" t="n">
-        <v>138.063179648229</v>
+        <v>121.6807557074624</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31078172055229</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>32.45854259780804</v>
       </c>
       <c r="C7" t="n">
-        <v>143.4284308519377</v>
+        <v>114.8026312915093</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="C8" t="n">
-        <v>106.0631132283042</v>
+        <v>78.77543578876406</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>45.04062117543515</v>
       </c>
       <c r="D9" t="n">
         <v>33.9468721174462</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.664574415927576</v>
+        <v>7.665938093191845</v>
       </c>
       <c r="C21" t="n">
-        <v>92.93296479312185</v>
+        <v>92.94949937995112</v>
       </c>
       <c r="D21" t="n">
-        <v>7.664574415927576</v>
+        <v>7.665938093191845</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.66704865954009</v>
+        <v>8.784678457600458</v>
       </c>
       <c r="C2" t="n">
-        <v>11.68868816676252</v>
+        <v>12.32191543600172</v>
       </c>
       <c r="D2" t="n">
-        <v>33.75739481052658</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>19.82148614874311</v>
       </c>
       <c r="C3" t="n">
-        <v>20.72469403665017</v>
+        <v>24.25898577193868</v>
       </c>
       <c r="D3" t="n">
-        <v>88.48492058376502</v>
+        <v>84.9211764173491</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.18307240354219</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="C4" t="n">
-        <v>59.38493688218531</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6197641766121</v>
+        <v>128.7375582055885</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.82936549257286</v>
+        <v>45.84761778832605</v>
       </c>
       <c r="C5" t="n">
-        <v>98.59201319898595</v>
+        <v>96.57943040527999</v>
       </c>
       <c r="D5" t="n">
-        <v>74.26921382627121</v>
+        <v>97.95387719122553</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.85292743747478</v>
+        <v>49.99255659565609</v>
       </c>
       <c r="C6" t="n">
-        <v>145.1072194261998</v>
+        <v>138.2644379275996</v>
       </c>
       <c r="D6" t="n">
-        <v>51.11960296013142</v>
+        <v>58.76741757621409</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.37491411649782</v>
+        <v>41.44153409166636</v>
       </c>
       <c r="C7" t="n">
-        <v>168.6406936447001</v>
+        <v>143.9075237316102</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C8" t="n">
-        <v>144.4494484643544</v>
+        <v>112.1548577331556</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>90.52499231318986</v>
+        <v>69.55780659359074</v>
       </c>
       <c r="D9" t="n">
         <v>35.05624702324509</v>
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.840077419095279</v>
+        <v>7.843253990933951</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9409967708517</v>
+        <v>100.9818951332746</v>
       </c>
       <c r="D21" t="n">
-        <v>8.82008709648219</v>
+        <v>8.823660739800694</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.977681844709581</v>
+        <v>10.62251015995049</v>
       </c>
       <c r="C2" t="n">
-        <v>14.61429632541802</v>
+        <v>12.59385955007808</v>
       </c>
       <c r="D2" t="n">
-        <v>42.83659757940108</v>
+        <v>38.07021247528281</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.70229376590174</v>
+        <v>23.6404847182632</v>
       </c>
       <c r="C3" t="n">
-        <v>32.17678100668921</v>
+        <v>34.98457944083508</v>
       </c>
       <c r="D3" t="n">
-        <v>92.45609004744337</v>
+        <v>90.49750337747099</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58773238414112</v>
+        <v>34.22961545626929</v>
       </c>
       <c r="C4" t="n">
-        <v>55.24981555189775</v>
+        <v>53.3864584092373</v>
       </c>
       <c r="D4" t="n">
-        <v>120.1227221008227</v>
+        <v>136.8418855041459</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.68839473378882</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="C5" t="n">
-        <v>102.0281301638498</v>
+        <v>93.266031903447</v>
       </c>
       <c r="D5" t="n">
-        <v>90.83620633543615</v>
+        <v>116.5089088014903</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.3736956890821</v>
+        <v>54.78250364467628</v>
       </c>
       <c r="C6" t="n">
-        <v>150.5009413133318</v>
+        <v>143.7789147823539</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>71.08442427369457</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.47767883027424</v>
+        <v>48.98724694650735</v>
       </c>
       <c r="C7" t="n">
-        <v>185.4089444332356</v>
+        <v>167.2633016156418</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>33.79666471869644</v>
       </c>
       <c r="C8" t="n">
-        <v>177.578524744163</v>
+        <v>146.7025594456009</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>17.74999849278232</v>
       </c>
       <c r="C9" t="n">
-        <v>128.2437391103523</v>
+        <v>98.40155414436202</v>
       </c>
       <c r="D9" t="n">
         <v>36.60937189136354</v>
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>71.17670855789376</v>
+        <v>58.64960785170445</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>42.11403126907541</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.999873455625451</v>
+        <v>8.004832261113393</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9982758328968</v>
+        <v>109.06583955767</v>
       </c>
       <c r="D21" t="n">
-        <v>9.999841819531813</v>
+        <v>10.00604032639174</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.217809121622549</v>
+        <v>9.553386910025711</v>
       </c>
       <c r="C2" t="n">
-        <v>10.05407823919158</v>
+        <v>8.663923489978101</v>
       </c>
       <c r="D2" t="n">
-        <v>35.15638528907828</v>
+        <v>31.32462399940298</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.13841073076557</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="C3" t="n">
-        <v>48.0467326458389</v>
+        <v>49.11192890494669</v>
       </c>
       <c r="D3" t="n">
-        <v>98.50856464412496</v>
+        <v>98.70000544645308</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.90908267859932</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="C4" t="n">
-        <v>80.62210322045232</v>
+        <v>75.75950684131787</v>
       </c>
       <c r="D4" t="n">
-        <v>111.0611907906247</v>
+        <v>131.2007631955437</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.06602344255857</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="C5" t="n">
-        <v>89.92808970900784</v>
+        <v>85.90292412159592</v>
       </c>
       <c r="D5" t="n">
-        <v>59.93569734426779</v>
+        <v>73.77833997414781</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.96860943565989</v>
+        <v>30.39000018496002</v>
       </c>
       <c r="C6" t="n">
-        <v>122.1235239220778</v>
+        <v>110.1687821274643</v>
       </c>
       <c r="D6" t="n">
-        <v>29.90698031447059</v>
+        <v>31.79880814055419</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>22.39759212468673</v>
       </c>
       <c r="C7" t="n">
-        <v>124.8635817646306</v>
+        <v>103.1247423494934</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>94.46376410262809</v>
+        <v>72.51679417419065</v>
       </c>
       <c r="D8" t="n">
         <v>26.95388322009618</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>44.70780870369548</v>
       </c>
       <c r="D9" t="n">
         <v>27.29062268265283</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
         <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.253912802501429</v>
+        <v>5.537057051952011</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612250714551515</v>
+        <v>3.631484758008952</v>
       </c>
       <c r="D2" t="n">
-        <v>23.73964123639212</v>
+        <v>21.96660488252238</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.89573912136737</v>
+        <v>29.97275741065512</v>
       </c>
       <c r="C3" t="n">
-        <v>44.55171081872026</v>
+        <v>42.19060759000668</v>
       </c>
       <c r="D3" t="n">
-        <v>104.2861498836174</v>
+        <v>101.8366893615216</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="C4" t="n">
-        <v>101.2466589912693</v>
+        <v>101.0169300284756</v>
       </c>
       <c r="D4" t="n">
-        <v>129.6309486164531</v>
+        <v>146.5287901019492</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="C5" t="n">
-        <v>118.6196663656209</v>
+        <v>112.3364810584413</v>
       </c>
       <c r="D5" t="n">
-        <v>79.00614649926207</v>
+        <v>95.22952731194061</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.67805317293184</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="C6" t="n">
-        <v>138.1034313041031</v>
+        <v>126.1486895094897</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30699359845555</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>149.057772188089</v>
+        <v>128.2172319223377</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>121.1673016581413</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
         <v>27.70492021384499</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>58.68593251676156</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>29.14219885286231</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2184,7 +2184,7 @@
         <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.181263472387165</v>
+        <v>4.904811530417065</v>
       </c>
       <c r="C2" t="n">
-        <v>7.823547455142832</v>
+        <v>5.198354093986861</v>
       </c>
       <c r="D2" t="n">
-        <v>22.70586090382023</v>
+        <v>27.54587708575701</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15389770985527</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C3" t="n">
-        <v>30.79251674370121</v>
+        <v>27.25331626989146</v>
       </c>
       <c r="D3" t="n">
-        <v>99.2350579452676</v>
+        <v>96.0787390761141</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.08395694314227</v>
+        <v>45.32041927114551</v>
       </c>
       <c r="C4" t="n">
-        <v>106.1347808107142</v>
+        <v>104.1310337463464</v>
       </c>
       <c r="D4" t="n">
-        <v>148.7750288492659</v>
+        <v>161.3718336424567</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.39262663290327</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="C5" t="n">
-        <v>151.1891464540088</v>
+        <v>147.7284857965388</v>
       </c>
       <c r="D5" t="n">
-        <v>102.7398972494287</v>
+        <v>120.9758608558132</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.63529824230149</v>
+        <v>40.33215918586747</v>
       </c>
       <c r="C6" t="n">
-        <v>163.0192062901829</v>
+        <v>151.7889943013036</v>
       </c>
       <c r="D6" t="n">
-        <v>49.22777513404782</v>
+        <v>56.95609306187872</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.91282974296706</v>
+        <v>29.70375853969149</v>
       </c>
       <c r="C7" t="n">
-        <v>174.2101483708923</v>
+        <v>153.1899482752638</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>156.2156946997524</v>
+        <v>128.9280172602124</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>96.29374182334411</v>
+        <v>78.76561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.504438393533613</v>
+        <v>2.949170103557418</v>
       </c>
       <c r="C2" t="n">
-        <v>3.73653176236336</v>
+        <v>2.461241494546754</v>
       </c>
       <c r="D2" t="n">
-        <v>15.83068173097982</v>
+        <v>19.20003985195487</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.87900835266616</v>
+        <v>23.55212742488098</v>
       </c>
       <c r="C3" t="n">
-        <v>32.63329368916398</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D3" t="n">
-        <v>98.49874716708248</v>
+        <v>98.25821897954202</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.92553570986004</v>
+        <v>49.81289676577891</v>
       </c>
       <c r="C4" t="n">
-        <v>105.8540009672996</v>
+        <v>101.412574353287</v>
       </c>
       <c r="D4" t="n">
-        <v>161.3335454819911</v>
+        <v>172.4498747371777</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.84070449666732</v>
+        <v>43.27053006467818</v>
       </c>
       <c r="C5" t="n">
-        <v>187.2929182776853</v>
+        <v>180.5188591183823</v>
       </c>
       <c r="D5" t="n">
-        <v>109.0967136344268</v>
+        <v>127.6517452446915</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.39000018496002</v>
+        <v>34.45541742824607</v>
       </c>
       <c r="C6" t="n">
-        <v>195.9450607952124</v>
+        <v>184.7551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>48.3422387048172</v>
+        <v>55.38627848278806</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>191.277832209223</v>
+        <v>163.131125528467</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9114253602314</v>
+        <v>97.2175664130404</v>
       </c>
       <c r="D8" t="n">
         <v>31.12631096314512</v>
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.838232612977529</v>
+        <v>3.815071578703105</v>
       </c>
       <c r="C2" t="n">
-        <v>3.23485868549324</v>
+        <v>5.388813148610742</v>
       </c>
       <c r="D2" t="n">
-        <v>15.78159434576748</v>
+        <v>17.95616551067416</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.97517856995335</v>
+        <v>16.95478285234242</v>
       </c>
       <c r="C3" t="n">
-        <v>23.61103228713579</v>
+        <v>17.57819264453914</v>
       </c>
       <c r="D3" t="n">
-        <v>90.19316158915447</v>
+        <v>92.28919293772141</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.10497455555895</v>
+        <v>47.92401418280805</v>
       </c>
       <c r="C4" t="n">
-        <v>93.97190850280045</v>
+        <v>84.42539382670446</v>
       </c>
       <c r="D4" t="n">
-        <v>170.9821619193287</v>
+        <v>179.9543541884404</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.06913291658734</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="C5" t="n">
-        <v>192.3734626471625</v>
+        <v>184.8876364022806</v>
       </c>
       <c r="D5" t="n">
-        <v>134.7448724078747</v>
+        <v>153.1280981698963</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>43.87430490278997</v>
       </c>
       <c r="C6" t="n">
-        <v>241.9929551152048</v>
+        <v>230.8432464380738</v>
       </c>
       <c r="D6" t="n">
-        <v>65.73095404243671</v>
+        <v>75.35109979635121</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>234.2165315498658</v>
+        <v>210.0223411264074</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>40.66300816219864</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>171.9040230136165</v>
+        <v>144.9501397935203</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>64.01093206459626</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.952696183746906</v>
+        <v>2.596722677732814</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91146278016854</v>
+        <v>2.734167356327367</v>
       </c>
       <c r="D2" t="n">
-        <v>11.69752389610075</v>
+        <v>12.98655863177681</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.311116211255</v>
+        <v>15.45270886484479</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06554041647306</v>
+        <v>19.27170743436489</v>
       </c>
       <c r="D3" t="n">
-        <v>84.79354921579701</v>
+        <v>87.85169331452583</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.95709050511617</v>
+        <v>43.11246868429443</v>
       </c>
       <c r="C4" t="n">
-        <v>81.89837523597318</v>
+        <v>69.48024852495527</v>
       </c>
       <c r="D4" t="n">
-        <v>175.34701221241</v>
+        <v>183.6938311939165</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.8060655895782</v>
+        <v>62.90548414961439</v>
       </c>
       <c r="C5" t="n">
-        <v>189.8700060013331</v>
+        <v>180.1261600366836</v>
       </c>
       <c r="D5" t="n">
-        <v>153.7171467924444</v>
+        <v>170.3086829942154</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.89317909334891</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="C6" t="n">
-        <v>274.113776502752</v>
+        <v>262.1590347081386</v>
       </c>
       <c r="D6" t="n">
-        <v>78.12846405166543</v>
+        <v>91.81402704886597</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>279.7303551187479</v>
+        <v>255.7158245251667</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>212.9607120052181</v>
+        <v>181.667503932351</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>84.09061785955626</v>
+        <v>72.33124385808797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.386047831947249</v>
+        <v>4.400193210434204</v>
       </c>
       <c r="C2" t="n">
-        <v>7.064656479760047</v>
+        <v>5.197372346282614</v>
       </c>
       <c r="D2" t="n">
-        <v>18.85740990317273</v>
+        <v>17.58702837387736</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.626036240139976</v>
+        <v>12.2963899956913</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79355524466769</v>
+        <v>15.35453409442012</v>
       </c>
       <c r="D3" t="n">
-        <v>76.20816554215865</v>
+        <v>79.47738539730054</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.49464627868692</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="C4" t="n">
-        <v>66.83836545282711</v>
+        <v>59.3594114418749</v>
       </c>
       <c r="D4" t="n">
-        <v>176.508419746534</v>
+        <v>184.5489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.33973543006097</v>
+        <v>63.3963580017378</v>
       </c>
       <c r="C5" t="n">
-        <v>173.1557513365312</v>
+        <v>157.6195939168254</v>
       </c>
       <c r="D5" t="n">
-        <v>173.695712573867</v>
+        <v>189.69820015309</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.51332484726341</v>
+        <v>64.00013283984957</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7867567062465</v>
+        <v>272.7049685471578</v>
       </c>
       <c r="D6" t="n">
-        <v>98.81781517096272</v>
+        <v>114.0329410913798</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.72750041104266</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C7" t="n">
-        <v>326.0227046170978</v>
+        <v>308.1166082393402</v>
       </c>
       <c r="D7" t="n">
-        <v>50.12509253572939</v>
+        <v>55.81432048183967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>275.5471281509522</v>
+        <v>241.5001177676729</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>146.4374875654542</v>
+        <v>127.6890516574529</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>55.51783267515713</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.556291095409447</v>
+        <v>7.642905877561418</v>
       </c>
       <c r="C2" t="n">
-        <v>13.70617969898972</v>
+        <v>9.025206645140928</v>
       </c>
       <c r="D2" t="n">
-        <v>7.703774235224722</v>
+        <v>3.783655652167207</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.447497026687298</v>
+        <v>3.181844309463912</v>
       </c>
       <c r="C2" t="n">
-        <v>4.125303853245097</v>
+        <v>2.993348750248525</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03015644139117</v>
+        <v>13.08473340220149</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.22414157620454</v>
+        <v>16.79279448114169</v>
       </c>
       <c r="C3" t="n">
-        <v>19.67913273162732</v>
+        <v>19.08517537055799</v>
       </c>
       <c r="D3" t="n">
-        <v>83.00185965554658</v>
+        <v>85.99128141497812</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.15977250054753</v>
+        <v>49.17476075801849</v>
       </c>
       <c r="C4" t="n">
-        <v>95.78421476484006</v>
+        <v>86.77373433526283</v>
       </c>
       <c r="D4" t="n">
-        <v>179.2524045799039</v>
+        <v>188.4288003714988</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.83946070705581</v>
+        <v>37.20823799095412</v>
       </c>
       <c r="C5" t="n">
-        <v>249.6829848825701</v>
+        <v>233.3614292994669</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1652246562084</v>
+        <v>170.6522946907018</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.18745705824891</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>267.9552731540118</v>
+        <v>253.7061869745735</v>
       </c>
       <c r="D6" t="n">
-        <v>76.15613291383359</v>
+        <v>87.82911311732816</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>193.7331832175443</v>
+        <v>169.8384258438812</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.363688618927824</v>
+        <v>7.266896506834891</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249805885235195</v>
+        <v>5.699045423152734</v>
       </c>
       <c r="D2" t="n">
-        <v>11.92528936348601</v>
+        <v>16.86348031584746</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.684941102394784</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C3" t="n">
-        <v>34.53788423540279</v>
+        <v>22.74218556887736</v>
       </c>
       <c r="D3" t="n">
-        <v>9.606401286055039</v>
+        <v>6.312637738306991</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39754450247447</v>
+        <v>13.39849114608988</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14008592471929</v>
+        <v>70.14504188247055</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576181706173467</v>
+        <v>1.576293076010574</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.50622196249286</v>
+        <v>4.969606878897355</v>
       </c>
       <c r="C2" t="n">
-        <v>6.517823008494575</v>
+        <v>5.592034923389832</v>
       </c>
       <c r="D2" t="n">
-        <v>14.98637870532756</v>
+        <v>29.5005367649124</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02350519163969</v>
+        <v>21.59844949342983</v>
       </c>
       <c r="C3" t="n">
-        <v>28.17615911188346</v>
+        <v>22.41820882647592</v>
       </c>
       <c r="D3" t="n">
-        <v>17.2983945488288</v>
+        <v>18.95263943048468</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.37158365829081</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="C4" t="n">
-        <v>53.16949216659876</v>
+        <v>35.18681946790993</v>
       </c>
       <c r="D4" t="n">
-        <v>20.10128424445344</v>
+        <v>18.37831702350029</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4388138325463</v>
+        <v>15.44047283583142</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13232980262671</v>
+        <v>86.14158529463846</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250276596325536</v>
+        <v>3.250625860175036</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.703553251046468</v>
+        <v>4.723188205131405</v>
       </c>
       <c r="C2" t="n">
-        <v>5.89735845941059</v>
+        <v>7.0175325899562</v>
       </c>
       <c r="D2" t="n">
-        <v>28.08583832309275</v>
+        <v>34.86186097780423</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22828955119978</v>
+        <v>19.12444527872787</v>
       </c>
       <c r="C3" t="n">
-        <v>26.73789872516188</v>
+        <v>22.01078352921349</v>
       </c>
       <c r="D3" t="n">
-        <v>25.2701859073129</v>
+        <v>38.15562452555229</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.61103228713579</v>
+        <v>31.90680038802134</v>
       </c>
       <c r="C4" t="n">
-        <v>62.72876956284995</v>
+        <v>46.96681017116741</v>
       </c>
       <c r="D4" t="n">
-        <v>24.26193101505142</v>
+        <v>23.75142220884308</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.28380720198534</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>58.29126993965438</v>
+        <v>39.34353924769093</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89421759431538</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72880979989631</v>
+        <v>16.73000961330477</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0457397793675</v>
+        <v>102.0530586411591</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182202449974079</v>
+        <v>4.182502403326192</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.069164307653782</v>
+        <v>5.022621254926682</v>
       </c>
       <c r="C2" t="n">
-        <v>6.127087422204344</v>
+        <v>6.820201301402592</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91515309127405</v>
+        <v>40.13090090649687</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52405765208533</v>
+        <v>24.94620916491145</v>
       </c>
       <c r="D3" t="n">
-        <v>40.99287539082557</v>
+        <v>56.16087742143878</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59300097556086</v>
+        <v>34.43381897875263</v>
       </c>
       <c r="C4" t="n">
-        <v>64.40068590318226</v>
+        <v>50.94877885959247</v>
       </c>
       <c r="D4" t="n">
-        <v>31.07722357793278</v>
+        <v>36.782159487311</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.80109043113217</v>
+        <v>31.90680038802134</v>
       </c>
       <c r="C5" t="n">
-        <v>89.38812847167209</v>
+        <v>64.94261063592651</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>30.9495963763807</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>53.69570893607505</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04663004746539</v>
+        <v>18.04833273692424</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7327769763218</v>
+        <v>117.7438849980295</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015543349155129</v>
+        <v>6.016110912308078</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.372524348266047</v>
+        <v>5.514476854754333</v>
       </c>
       <c r="C2" t="n">
-        <v>4.599487994396307</v>
+        <v>6.389214059238242</v>
       </c>
       <c r="D2" t="n">
-        <v>29.24822760492098</v>
+        <v>36.1970378555799</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56699250916493</v>
+        <v>15.33980787885641</v>
       </c>
       <c r="C3" t="n">
-        <v>22.61455836732528</v>
+        <v>24.20989838672634</v>
       </c>
       <c r="D3" t="n">
-        <v>44.94440990041898</v>
+        <v>69.77280934082081</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.28821721888784</v>
+        <v>24.5299481383108</v>
       </c>
       <c r="C4" t="n">
-        <v>51.90598287123311</v>
+        <v>47.83467514172159</v>
       </c>
       <c r="D4" t="n">
-        <v>38.32644862609123</v>
+        <v>48.54938747041327</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.53677931451153</v>
+        <v>25.47635292520474</v>
       </c>
       <c r="C5" t="n">
-        <v>78.22074833586463</v>
+        <v>59.15029918087033</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>67.05925868628265</v>
+        <v>48.42274201656544</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>31.20092378866788</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049956408720004</v>
+        <v>7.050066738188097</v>
       </c>
       <c r="C21" t="n">
-        <v>66.09334133175004</v>
+        <v>66.0943756705134</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406222755450003</v>
+        <v>4.406291711367561</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.220934291184538</v>
+        <v>5.037347470490384</v>
       </c>
       <c r="C2" t="n">
-        <v>7.231553589482005</v>
+        <v>3.049308369390593</v>
       </c>
       <c r="D2" t="n">
-        <v>33.72696063169492</v>
+        <v>25.73651606683013</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.02765316663493</v>
+        <v>17.74018101573986</v>
       </c>
       <c r="C3" t="n">
-        <v>19.62022786937251</v>
+        <v>24.67622854624358</v>
       </c>
       <c r="D3" t="n">
-        <v>58.64960785170445</v>
+        <v>83.3209276594268</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.14179794223482</v>
+        <v>28.1162725019244</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98179842863836</v>
+        <v>55.82413795888213</v>
       </c>
       <c r="D4" t="n">
-        <v>52.62069519992479</v>
+        <v>73.8578615381918</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.62990647769474</v>
+        <v>32.07860623626453</v>
       </c>
       <c r="C5" t="n">
-        <v>89.24086631603508</v>
+        <v>76.25725292737101</v>
       </c>
       <c r="D5" t="n">
-        <v>36.74190783143688</v>
+        <v>40.66889864842413</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.92456965768902</v>
+        <v>26.48558956517046</v>
       </c>
       <c r="C6" t="n">
-        <v>100.9109012764169</v>
+        <v>75.31084814047708</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>69.46846755250429</v>
+        <v>50.90361846519711</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>31.96079651175491</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268954491155306</v>
+        <v>7.268194402407961</v>
       </c>
       <c r="C21" t="n">
-        <v>75.4154028457363</v>
+        <v>75.4075169249826</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451715868366479</v>
+        <v>5.45114580180597</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.293182710671302</v>
+        <v>5.3711416899343</v>
       </c>
       <c r="C2" t="n">
-        <v>6.57770961845363</v>
+        <v>5.436918786118836</v>
       </c>
       <c r="D2" t="n">
-        <v>37.25045314223672</v>
+        <v>22.93460811890974</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.89373456822987</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>24.68604602328605</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="D3" t="n">
-        <v>72.02101158354601</v>
+        <v>84.57756472086271</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.99988649347554</v>
+        <v>31.5494442236755</v>
       </c>
       <c r="C4" t="n">
-        <v>51.62520302781852</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>70.19496085364693</v>
+        <v>99.01318296410781</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>37.94454876913922</v>
       </c>
       <c r="C5" t="n">
-        <v>96.23581870879362</v>
+        <v>90.63985679458678</v>
       </c>
       <c r="D5" t="n">
-        <v>47.36932672990861</v>
+        <v>57.89857085795565</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.45792070300229</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>122.3247822014483</v>
+        <v>100.7096429970463</v>
       </c>
       <c r="D6" t="n">
-        <v>37.23278168356029</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>111.329207913884</v>
+        <v>82.58363513353744</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>64.33883579781471</v>
+        <v>48.81740459367264</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
         <v>32.9484347022272</v>
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474282063277497</v>
+        <v>7.473894675241597</v>
       </c>
       <c r="C21" t="n">
-        <v>84.08567321187184</v>
+        <v>84.08131509646797</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539996805367809</v>
+        <v>6.539657840836397</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762099728</v>
+        <v>10.8449761789451</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907151595916</v>
+        <v>37.78907140784382</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.608143797285281</v>
+        <v>5.242532740677968</v>
       </c>
       <c r="C2" t="n">
-        <v>7.567311304334415</v>
+        <v>12.62920246743097</v>
       </c>
       <c r="D2" t="n">
-        <v>27.52820562708056</v>
+        <v>21.55132560362598</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>16.3608254912731</v>
       </c>
       <c r="C3" t="n">
-        <v>19.25698121880119</v>
+        <v>31.1508546557513</v>
       </c>
       <c r="D3" t="n">
-        <v>83.0902169489288</v>
+        <v>51.11960296013142</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.78742807873073</v>
+        <v>33.01715704152448</v>
       </c>
       <c r="C4" t="n">
-        <v>50.25959197121121</v>
+        <v>67.99977298695107</v>
       </c>
       <c r="D4" t="n">
-        <v>115.9365498899143</v>
+        <v>67.19572161717294</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.55876297909924</v>
+        <v>39.61351986635881</v>
       </c>
       <c r="C5" t="n">
-        <v>100.4082464518426</v>
+        <v>121.7367153266045</v>
       </c>
       <c r="D5" t="n">
-        <v>79.03069019186825</v>
+        <v>53.06346341454012</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.83405324691584</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6807557074624</v>
+        <v>157.2229678443097</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>41.53970886209105</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>26.29022177202533</v>
       </c>
       <c r="C7" t="n">
-        <v>114.8026312915093</v>
+        <v>148.8182257482527</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.44074796594459</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>78.77543578876406</v>
+        <v>96.13273519984767</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>45.04062117543515</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.665938093191845</v>
+        <v>7.677503107847255</v>
       </c>
       <c r="C21" t="n">
-        <v>92.94949937995112</v>
+        <v>93.08972518264797</v>
       </c>
       <c r="D21" t="n">
-        <v>7.665938093191845</v>
+        <v>7.677503107847255</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.784678457600458</v>
+        <v>6.014186436215961</v>
       </c>
       <c r="C2" t="n">
-        <v>12.32191543600172</v>
+        <v>8.010079518949725</v>
       </c>
       <c r="D2" t="n">
-        <v>35.33800861436394</v>
+        <v>17.9129686116873</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.82148614874311</v>
+        <v>16.81733817374786</v>
       </c>
       <c r="C3" t="n">
-        <v>24.25898577193868</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D3" t="n">
-        <v>84.9211764173491</v>
+        <v>55.38529673508381</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.99163160121406</v>
+        <v>31.72812230584842</v>
       </c>
       <c r="C4" t="n">
-        <v>48.63872651149973</v>
+        <v>72.03279255599696</v>
       </c>
       <c r="D4" t="n">
-        <v>128.7375582055885</v>
+        <v>75.87437132271475</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.84761778832605</v>
+        <v>44.32590884674349</v>
       </c>
       <c r="C5" t="n">
-        <v>96.57943040527999</v>
+        <v>123.3565990386117</v>
       </c>
       <c r="D5" t="n">
-        <v>97.95387719122553</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.99255659565609</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="C6" t="n">
-        <v>138.2644379275996</v>
+        <v>172.8808619793421</v>
       </c>
       <c r="D6" t="n">
-        <v>58.76741757621409</v>
+        <v>47.93972214607601</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.44153409166636</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>143.9075237316102</v>
+        <v>186.2473569726624</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.45180923259856</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="C8" t="n">
-        <v>112.1548577331556</v>
+        <v>141.9459918185251</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="C9" t="n">
-        <v>69.55780659359074</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.843253990933951</v>
+        <v>7.854684374605644</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9818951332746</v>
+        <v>101.1290613230477</v>
       </c>
       <c r="D21" t="n">
-        <v>8.823660739800694</v>
+        <v>8.83651992143135</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.62251015995049</v>
+        <v>6.509969026860599</v>
       </c>
       <c r="C2" t="n">
-        <v>12.59385955007808</v>
+        <v>17.92474958413826</v>
       </c>
       <c r="D2" t="n">
-        <v>38.07021247528281</v>
+        <v>15.45958109877452</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6404847182632</v>
+        <v>17.92671307954676</v>
       </c>
       <c r="C3" t="n">
-        <v>34.98457944083508</v>
+        <v>35.5343581552133</v>
       </c>
       <c r="D3" t="n">
-        <v>90.49750337747099</v>
+        <v>55.93998418798326</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.22961545626929</v>
+        <v>31.07722357793278</v>
       </c>
       <c r="C4" t="n">
-        <v>53.3864584092373</v>
+        <v>84.336054785618</v>
       </c>
       <c r="D4" t="n">
-        <v>136.8418855041459</v>
+        <v>82.63861300497526</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.97662764820988</v>
+        <v>45.33220024359647</v>
       </c>
       <c r="C5" t="n">
-        <v>93.266031903447</v>
+        <v>125.8600556844411</v>
       </c>
       <c r="D5" t="n">
-        <v>116.5089088014903</v>
+        <v>72.72296119208249</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.78250364467628</v>
+        <v>50.67683474551611</v>
       </c>
       <c r="C6" t="n">
-        <v>143.7789147823539</v>
+        <v>181.4947163364036</v>
       </c>
       <c r="D6" t="n">
-        <v>71.08442427369457</v>
+        <v>54.17872880656449</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.98724694650735</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="C7" t="n">
-        <v>167.2633016156418</v>
+        <v>214.6336100932547</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>44.73529763941441</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.79666471869644</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7025594456009</v>
+        <v>185.4226889010951</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>14.31093628480575</v>
       </c>
       <c r="C9" t="n">
-        <v>98.40155414436202</v>
+        <v>120.3671772791802</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>58.64960785170445</v>
+        <v>65.19786503903067</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>39.80397892098267</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.004832261113393</v>
+        <v>8.016115662009975</v>
       </c>
       <c r="C21" t="n">
-        <v>109.06583955767</v>
+        <v>109.2195758948859</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00604032639174</v>
+        <v>10.02014457751247</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.553386910025711</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C2" t="n">
-        <v>8.663923489978101</v>
+        <v>12.33173291304418</v>
       </c>
       <c r="D2" t="n">
-        <v>31.32462399940298</v>
+        <v>12.90409182462007</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.11939767148639</v>
+        <v>21.48554850744145</v>
       </c>
       <c r="C3" t="n">
-        <v>49.11192890494669</v>
+        <v>57.54023294590556</v>
       </c>
       <c r="D3" t="n">
-        <v>98.70000544645308</v>
+        <v>60.78000036992003</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.56448923440869</v>
+        <v>21.77320058478576</v>
       </c>
       <c r="C4" t="n">
-        <v>75.75950684131787</v>
+        <v>108.9681046851705</v>
       </c>
       <c r="D4" t="n">
-        <v>131.2007631955437</v>
+        <v>80.07330625377834</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>28.54431450097602</v>
       </c>
       <c r="C5" t="n">
-        <v>85.90292412159592</v>
+        <v>108.4340339340602</v>
       </c>
       <c r="D5" t="n">
-        <v>73.77833997414781</v>
+        <v>51.90990986205011</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.39000018496002</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>110.1687821274643</v>
+        <v>141.3638154299067</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79880814055419</v>
+        <v>29.46421209985528</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>103.1247423494934</v>
+        <v>130.3731498808637</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.72750041104266</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>72.51679417419065</v>
+        <v>88.70581381722054</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>49.69999577979051</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.537057051952011</v>
+        <v>3.701188845010475</v>
       </c>
       <c r="C2" t="n">
-        <v>3.631484758008952</v>
+        <v>5.432010047597601</v>
       </c>
       <c r="D2" t="n">
-        <v>21.96660488252238</v>
+        <v>8.840638076742527</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.97275741065512</v>
+        <v>21.69171552533328</v>
       </c>
       <c r="C3" t="n">
-        <v>42.19060759000668</v>
+        <v>53.87831400906496</v>
       </c>
       <c r="D3" t="n">
-        <v>101.8366893615216</v>
+        <v>58.36980975599411</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>30.09449412598173</v>
       </c>
       <c r="C4" t="n">
-        <v>101.0169300284756</v>
+        <v>129.6054231761427</v>
       </c>
       <c r="D4" t="n">
-        <v>146.5287901019492</v>
+        <v>89.63258365002955</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.64940256305943</v>
+        <v>31.857713002809</v>
       </c>
       <c r="C5" t="n">
-        <v>112.3364810584413</v>
+        <v>152.1463504656495</v>
       </c>
       <c r="D5" t="n">
-        <v>95.22952731194061</v>
+        <v>64.05903770210439</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.82397372796611</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1486895094897</v>
+        <v>160.8456168729805</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>35.30070220160257</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>128.2172319223377</v>
+        <v>162.9514656985898</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>115.6596970373167</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>49.81093327037041</v>
+        <v>55.1359328182051</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.904811530417065</v>
+        <v>3.786600895279947</v>
       </c>
       <c r="C2" t="n">
-        <v>5.198354093986861</v>
+        <v>6.054438092090079</v>
       </c>
       <c r="D2" t="n">
-        <v>27.54587708575701</v>
+        <v>10.56164180228719</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.36697801940583</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="C3" t="n">
-        <v>27.25331626989146</v>
+        <v>36.42283982755666</v>
       </c>
       <c r="D3" t="n">
-        <v>96.0787390761141</v>
+        <v>52.51859343868312</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.32041927114551</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="C4" t="n">
-        <v>104.1310337463464</v>
+        <v>133.2810865808427</v>
       </c>
       <c r="D4" t="n">
-        <v>161.3718336424567</v>
+        <v>97.03496134005049</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.55247158224626</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>147.7284857965388</v>
+        <v>193.6988220478957</v>
       </c>
       <c r="D5" t="n">
-        <v>120.9758608558132</v>
+        <v>78.7361658805942</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.33215918586747</v>
+        <v>36.46800022195202</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7889943013036</v>
+        <v>200.0104780384985</v>
       </c>
       <c r="D6" t="n">
-        <v>56.95609306187872</v>
+        <v>44.84034464376883</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.70375853969149</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="C7" t="n">
-        <v>153.1899482752638</v>
+        <v>195.0506886366435</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>128.9280172602124</v>
+        <v>161.4729536559941</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>78.76561831172157</v>
+        <v>92.85467961536754</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.949170103557418</v>
+        <v>2.264891953697392</v>
       </c>
       <c r="C2" t="n">
-        <v>2.461241494546754</v>
+        <v>2.913827186204533</v>
       </c>
       <c r="D2" t="n">
-        <v>19.20003985195487</v>
+        <v>7.385687979048754</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.55212742488098</v>
+        <v>16.93023915973625</v>
       </c>
       <c r="C3" t="n">
-        <v>26.05067533218912</v>
+        <v>33.35487825178538</v>
       </c>
       <c r="D3" t="n">
-        <v>98.25821897954202</v>
+        <v>51.36994862471436</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.81289676577891</v>
+        <v>39.06668639509333</v>
       </c>
       <c r="C4" t="n">
-        <v>101.412574353287</v>
+        <v>131.0731359939917</v>
       </c>
       <c r="D4" t="n">
-        <v>172.4498747371777</v>
+        <v>102.5484564471006</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.27053006467818</v>
+        <v>39.34353924769093</v>
       </c>
       <c r="C5" t="n">
-        <v>180.5188591183823</v>
+        <v>235.4721868635975</v>
       </c>
       <c r="D5" t="n">
-        <v>127.6517452446915</v>
+        <v>83.12948685709868</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="C6" t="n">
-        <v>184.7551004622073</v>
+        <v>241.8722001475825</v>
       </c>
       <c r="D6" t="n">
-        <v>55.38627848278806</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>163.131125528467</v>
+        <v>207.5071035081271</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>97.2175664130404</v>
+        <v>115.9100427018997</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.815071578703105</v>
+        <v>3.038509144643878</v>
       </c>
       <c r="C2" t="n">
-        <v>5.388813148610742</v>
+        <v>11.14185469549705</v>
       </c>
       <c r="D2" t="n">
-        <v>17.95616551067416</v>
+        <v>7.153995520846507</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95478285234242</v>
+        <v>12.41910845872215</v>
       </c>
       <c r="C3" t="n">
-        <v>17.57819264453914</v>
+        <v>22.04023596034089</v>
       </c>
       <c r="D3" t="n">
-        <v>92.28919293772141</v>
+        <v>46.4464838879166</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.92401418280805</v>
+        <v>36.25888796094745</v>
       </c>
       <c r="C4" t="n">
-        <v>84.42539382670446</v>
+        <v>108.7383757223767</v>
       </c>
       <c r="D4" t="n">
-        <v>179.9543541884404</v>
+        <v>104.1820846269673</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.13142499031139</v>
+        <v>47.46750150033328</v>
       </c>
       <c r="C5" t="n">
-        <v>184.8876364022806</v>
+        <v>240.160032151376</v>
       </c>
       <c r="D5" t="n">
-        <v>153.1280981698963</v>
+        <v>97.02121687219106</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.87430490278997</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>230.8432464380738</v>
+        <v>301.6056574647754</v>
       </c>
       <c r="D6" t="n">
-        <v>75.35109979635121</v>
+        <v>56.31206656789281</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>210.0223411264074</v>
+        <v>271.166569894603</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>144.9501397935203</v>
+        <v>179.2474958413826</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>73.21874378272709</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.596722677732814</v>
+        <v>1.972331137831842</v>
       </c>
       <c r="C2" t="n">
-        <v>2.734167356327367</v>
+        <v>5.550801519811467</v>
       </c>
       <c r="D2" t="n">
-        <v>12.98655863177681</v>
+        <v>5.69708192774424</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.45270886484479</v>
+        <v>11.64352777236717</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27170743436489</v>
+        <v>32.088423713307</v>
       </c>
       <c r="D3" t="n">
-        <v>87.85169331452583</v>
+        <v>43.08399800087128</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.11246868429443</v>
+        <v>32.07271575003904</v>
       </c>
       <c r="C4" t="n">
-        <v>69.48024852495527</v>
+        <v>88.31802347404307</v>
       </c>
       <c r="D4" t="n">
-        <v>183.6938311939165</v>
+        <v>104.0799828657256</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.90548414961439</v>
+        <v>51.66447293598841</v>
       </c>
       <c r="C5" t="n">
-        <v>180.1261600366836</v>
+        <v>233.3368856068607</v>
       </c>
       <c r="D5" t="n">
-        <v>170.3086829942154</v>
+        <v>105.9060335956247</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>45.52462279362885</v>
       </c>
       <c r="C6" t="n">
-        <v>262.1590347081386</v>
+        <v>341.8170616830205</v>
       </c>
       <c r="D6" t="n">
-        <v>91.81402704886597</v>
+        <v>66.17372225705202</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>255.7158245251667</v>
+        <v>331.4124995134127</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>181.667503932351</v>
+        <v>226.8131721121406</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>83.09218044433726</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.400193210434204</v>
+        <v>2.816634163484099</v>
       </c>
       <c r="C2" t="n">
-        <v>5.197372346282614</v>
+        <v>5.106069809787661</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58702837387736</v>
+        <v>10.30736914688726</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.2963899956913</v>
+        <v>9.287333282174826</v>
       </c>
       <c r="C3" t="n">
-        <v>15.35453409442012</v>
+        <v>27.10605411425443</v>
       </c>
       <c r="D3" t="n">
-        <v>79.47738539730054</v>
+        <v>38.98520133564084</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.59071868498287</v>
+        <v>27.32498385230147</v>
       </c>
       <c r="C4" t="n">
-        <v>59.3594114418749</v>
+        <v>84.45091926701488</v>
       </c>
       <c r="D4" t="n">
-        <v>184.5489334443154</v>
+        <v>100.9786418680099</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.3963580017378</v>
+        <v>50.75635630956011</v>
       </c>
       <c r="C5" t="n">
-        <v>157.6195939168254</v>
+        <v>203.4917553977577</v>
       </c>
       <c r="D5" t="n">
-        <v>189.69820015309</v>
+        <v>115.3308115563941</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.00013283984957</v>
+        <v>54.17872880656449</v>
       </c>
       <c r="C6" t="n">
-        <v>272.7049685471578</v>
+        <v>354.2950750039975</v>
       </c>
       <c r="D6" t="n">
-        <v>114.0329410913798</v>
+        <v>78.73223888977722</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>27.18852092141116</v>
       </c>
       <c r="C7" t="n">
-        <v>308.1166082393402</v>
+        <v>395.4911721696021</v>
       </c>
       <c r="D7" t="n">
-        <v>55.81432048183967</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>241.5001177676729</v>
+        <v>309.5106899793706</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>127.6890516574529</v>
+        <v>152.3171745661883</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>53.80959166976768</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.642905877561418</v>
+        <v>4.635812659453438</v>
       </c>
       <c r="C2" t="n">
-        <v>9.025206645140928</v>
+        <v>9.196030745679874</v>
       </c>
       <c r="D2" t="n">
-        <v>3.783655652167207</v>
+        <v>6.475607857211961</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.181844309463912</v>
+        <v>2.036144738607885</v>
       </c>
       <c r="C2" t="n">
-        <v>2.993348750248525</v>
+        <v>2.98254952550181</v>
       </c>
       <c r="D2" t="n">
-        <v>13.08473340220149</v>
+        <v>7.668431317871836</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.79279448114169</v>
+        <v>12.5271007061893</v>
       </c>
       <c r="C3" t="n">
-        <v>19.08517537055799</v>
+        <v>29.1922679857789</v>
       </c>
       <c r="D3" t="n">
-        <v>85.99128141497812</v>
+        <v>42.91710089114932</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.17476075801849</v>
+        <v>38.09671966329748</v>
       </c>
       <c r="C4" t="n">
-        <v>86.77373433526283</v>
+        <v>121.6925366799134</v>
       </c>
       <c r="D4" t="n">
-        <v>188.4288003714988</v>
+        <v>104.5394407913131</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.20823799095412</v>
+        <v>31.44047022850411</v>
       </c>
       <c r="C5" t="n">
-        <v>233.3614292994669</v>
+        <v>300.414797499524</v>
       </c>
       <c r="D5" t="n">
-        <v>170.6522946907018</v>
+        <v>107.0104997629024</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.80381469006666</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>253.7061869745735</v>
+        <v>326.440929139107</v>
       </c>
       <c r="D6" t="n">
-        <v>87.82911311732816</v>
+        <v>65.04667589257669</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>169.8384258438812</v>
+        <v>217.6279405912074</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>112.2383062880166</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.266896506834891</v>
+        <v>6.343071917138642</v>
       </c>
       <c r="C2" t="n">
-        <v>5.699045423152734</v>
+        <v>9.610328276872027</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86348031584746</v>
+        <v>12.23748513343649</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22828955119978</v>
+        <v>9.851838212116743</v>
       </c>
       <c r="C3" t="n">
-        <v>22.74218556887736</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="D3" t="n">
-        <v>6.312637738306991</v>
+        <v>8.575566196595888</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39849114608988</v>
+        <v>13.39851595038474</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14504188247055</v>
+        <v>70.14517174024955</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576293076010574</v>
+        <v>1.576295994162911</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.969606878897355</v>
+        <v>4.62599518241097</v>
       </c>
       <c r="C2" t="n">
-        <v>5.592034923389832</v>
+        <v>8.93881284716721</v>
       </c>
       <c r="D2" t="n">
-        <v>29.5005367649124</v>
+        <v>15.53517567200153</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.59844949342983</v>
+        <v>17.04804888424586</v>
       </c>
       <c r="C3" t="n">
-        <v>22.41820882647592</v>
+        <v>32.12278488295564</v>
       </c>
       <c r="D3" t="n">
-        <v>18.95263943048468</v>
+        <v>16.78297700409922</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.76119862815655</v>
+        <v>11.56302446061893</v>
       </c>
       <c r="C4" t="n">
-        <v>35.18681946790993</v>
+        <v>35.83771819582557</v>
       </c>
       <c r="D4" t="n">
-        <v>18.37831702350029</v>
+        <v>19.56524999793468</v>
       </c>
     </row>
     <row r="5">
@@ -4871,7 +4871,7 @@
         <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44047283583142</v>
+        <v>15.44151358579321</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14158529463846</v>
+        <v>86.14739158389898</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250625860175036</v>
+        <v>3.25084496543015</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.723188205131405</v>
+        <v>4.51211244871834</v>
       </c>
       <c r="C2" t="n">
-        <v>7.0175325899562</v>
+        <v>5.64504929941916</v>
       </c>
       <c r="D2" t="n">
-        <v>34.86186097780423</v>
+        <v>17.35042717715388</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.12444527872787</v>
+        <v>16.47372647726148</v>
       </c>
       <c r="C3" t="n">
-        <v>22.01078352921349</v>
+        <v>33.73775985644163</v>
       </c>
       <c r="D3" t="n">
-        <v>38.15562452555229</v>
+        <v>25.314364554004</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.90680038802134</v>
+        <v>23.72589676853267</v>
       </c>
       <c r="C4" t="n">
-        <v>46.96681017116741</v>
+        <v>62.09063355508952</v>
       </c>
       <c r="D4" t="n">
-        <v>23.75142220884308</v>
+        <v>23.58550684682537</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.95340019401067</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C5" t="n">
-        <v>39.34353924769093</v>
+        <v>40.0307626406637</v>
       </c>
       <c r="D5" t="n">
-        <v>29.30516897176729</v>
+        <v>29.47697482001049</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>38.05254101660637</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73000961330477</v>
+        <v>16.73368405342321</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0530586411591</v>
+        <v>102.0754727258816</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182502403326192</v>
+        <v>4.183421013355803</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.022621254926682</v>
+        <v>4.982369599052562</v>
       </c>
       <c r="C2" t="n">
-        <v>6.820201301402592</v>
+        <v>8.646252031301659</v>
       </c>
       <c r="D2" t="n">
-        <v>40.13090090649687</v>
+        <v>14.62116855934775</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48492661263569</v>
+        <v>16.06139244147782</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94620916491145</v>
+        <v>26.89497835784137</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16087742143878</v>
+        <v>32.86891313818321</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>27.89930625928586</v>
       </c>
       <c r="C4" t="n">
-        <v>50.94877885959247</v>
+        <v>74.57257386688347</v>
       </c>
       <c r="D4" t="n">
-        <v>36.782159487311</v>
+        <v>30.56671477172444</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.90680038802134</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>64.94261063592651</v>
+        <v>80.33150589999526</v>
       </c>
       <c r="D5" t="n">
-        <v>30.9495963763807</v>
+        <v>31.02322745419922</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.56480802957818</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.64158963915446</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
         <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
         <v>42.26718391093791</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04833273692424</v>
+        <v>18.05644347296937</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7438849980295</v>
+        <v>117.7967978950859</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016110912308078</v>
+        <v>6.018814490989792</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.514476854754333</v>
+        <v>5.339725763398402</v>
       </c>
       <c r="C2" t="n">
-        <v>6.389214059238242</v>
+        <v>7.792131528606935</v>
       </c>
       <c r="D2" t="n">
-        <v>36.1970378555799</v>
+        <v>23.43628119577986</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.33980787885641</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C3" t="n">
-        <v>24.20989838672634</v>
+        <v>28.86829124337746</v>
       </c>
       <c r="D3" t="n">
-        <v>69.77280934082081</v>
+        <v>34.49861432723292</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.5299481383108</v>
+        <v>21.63281066307847</v>
       </c>
       <c r="C4" t="n">
-        <v>47.83467514172159</v>
+        <v>58.97652983721864</v>
       </c>
       <c r="D4" t="n">
-        <v>48.54938747041327</v>
+        <v>34.58697162061513</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.47635292520474</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="C5" t="n">
-        <v>59.15029918087033</v>
+        <v>82.56498192715677</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>28.00435326364027</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.49688751153591</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>48.42274201656544</v>
+        <v>56.714583126634</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.852943133008</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050066738188097</v>
+        <v>7.055580367331901</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0943756705134</v>
+        <v>66.14606594373657</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406291711367561</v>
+        <v>4.409737729582438</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.037347470490384</v>
+        <v>5.44182752464007</v>
       </c>
       <c r="C2" t="n">
-        <v>3.049308369390593</v>
+        <v>5.972953032637593</v>
       </c>
       <c r="D2" t="n">
-        <v>25.73651606683013</v>
+        <v>17.37202562664731</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.74018101573986</v>
+        <v>17.37202562664731</v>
       </c>
       <c r="C3" t="n">
-        <v>24.67622854624358</v>
+        <v>29.88930885579414</v>
       </c>
       <c r="D3" t="n">
-        <v>83.3209276594268</v>
+        <v>45.84761778832605</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.1162725019244</v>
+        <v>26.07423727709104</v>
       </c>
       <c r="C4" t="n">
-        <v>55.82413795888213</v>
+        <v>67.46373874043232</v>
       </c>
       <c r="D4" t="n">
-        <v>73.8578615381918</v>
+        <v>44.31216437888403</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.07860623626453</v>
+        <v>27.34167356327368</v>
       </c>
       <c r="C5" t="n">
-        <v>76.25725292737101</v>
+        <v>98.91108120286617</v>
       </c>
       <c r="D5" t="n">
-        <v>40.66889864842413</v>
+        <v>34.90113088597411</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.48558956517046</v>
+        <v>19.96482131356314</v>
       </c>
       <c r="C6" t="n">
-        <v>75.31084814047708</v>
+        <v>100.588888029424</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>50.90361846519711</v>
+        <v>58.09001166028376</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>26.78698611037422</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268194402407961</v>
+        <v>7.276369584524546</v>
       </c>
       <c r="C21" t="n">
-        <v>75.4075169249826</v>
+        <v>75.49233443944217</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45114580180597</v>
+        <v>5.45727718839341</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.3711416899343</v>
+        <v>4.350124077517616</v>
       </c>
       <c r="C2" t="n">
-        <v>5.436918786118836</v>
+        <v>9.077239273466008</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93460811890974</v>
+        <v>17.31213901668826</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="C3" t="n">
-        <v>17.02350519163969</v>
+        <v>26.14394136409256</v>
       </c>
       <c r="D3" t="n">
-        <v>84.57756472086271</v>
+        <v>49.10702016642546</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.5494442236755</v>
+        <v>30.61776565234527</v>
       </c>
       <c r="C4" t="n">
-        <v>59.29559784109885</v>
+        <v>71.11387670482196</v>
       </c>
       <c r="D4" t="n">
-        <v>99.01318296410781</v>
+        <v>57.34290165735195</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.94454876913922</v>
+        <v>33.69848994827177</v>
       </c>
       <c r="C5" t="n">
-        <v>90.63985679458678</v>
+        <v>113.7109278443868</v>
       </c>
       <c r="D5" t="n">
-        <v>57.89857085795565</v>
+        <v>42.68148144213009</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>29.38370878810704</v>
       </c>
       <c r="C6" t="n">
-        <v>100.7096429970463</v>
+        <v>131.9449279553629</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>37.0315234041897</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>82.58363513353744</v>
+        <v>105.0411138681832</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>48.81740459367264</v>
+        <v>54.40845776935822</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473894675241597</v>
+        <v>7.484269812717949</v>
       </c>
       <c r="C21" t="n">
-        <v>84.08131509646797</v>
+        <v>84.19803539307694</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539657840836397</v>
+        <v>6.548736086128206</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_98_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449761789451</v>
+        <v>10.84497646706181</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907140784382</v>
+        <v>37.78907241177991</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.242532740677968</v>
+        <v>1.0004009106275</v>
       </c>
       <c r="C2" t="n">
-        <v>12.62920246743097</v>
+        <v>2.246238747316702</v>
       </c>
       <c r="D2" t="n">
-        <v>21.55132560362598</v>
+        <v>11.69261515757951</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1508546557513</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="D3" t="n">
-        <v>51.11960296013142</v>
+        <v>55.38529673508381</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.01715704152448</v>
+        <v>15.00895890252524</v>
       </c>
       <c r="C4" t="n">
-        <v>67.99977298695107</v>
+        <v>105.1775767990735</v>
       </c>
       <c r="D4" t="n">
-        <v>67.19572161717294</v>
+        <v>65.30683903420207</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61351986635881</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7367153266045</v>
+        <v>122.6939193382452</v>
       </c>
       <c r="D5" t="n">
-        <v>53.06346341454012</v>
+        <v>45.0622196249286</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>8.694357668809754</v>
       </c>
       <c r="C6" t="n">
-        <v>157.2229678443097</v>
+        <v>78.00770908404307</v>
       </c>
       <c r="D6" t="n">
-        <v>41.53970886209105</v>
+        <v>29.38370878810704</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8182257482527</v>
+        <v>43.17824578047897</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>96.13273519984767</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.677503107847255</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.08972518264797</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.677503107847255</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.014186436215961</v>
+        <v>1.341067364001143</v>
       </c>
       <c r="C2" t="n">
-        <v>8.010079518949725</v>
+        <v>7.489753235698917</v>
       </c>
       <c r="D2" t="n">
-        <v>17.9129686116873</v>
+        <v>21.75356563070082</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.81733817374786</v>
+        <v>5.959208564778139</v>
       </c>
       <c r="C3" t="n">
-        <v>40.00131020953629</v>
+        <v>16.70934592628072</v>
       </c>
       <c r="D3" t="n">
-        <v>55.38529673508381</v>
+        <v>52.42041866825843</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.72812230584842</v>
+        <v>16.47667172037422</v>
       </c>
       <c r="C4" t="n">
-        <v>72.03279255599696</v>
+        <v>86.722683454642</v>
       </c>
       <c r="D4" t="n">
-        <v>75.87437132271475</v>
+        <v>77.67391486459914</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.32590884674349</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="C5" t="n">
-        <v>123.3565990386117</v>
+        <v>162.1356333563608</v>
       </c>
       <c r="D5" t="n">
-        <v>62.63550353094652</v>
+        <v>57.60404654668161</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>172.8808619793421</v>
+        <v>140.5990339682985</v>
       </c>
       <c r="D6" t="n">
-        <v>47.93972214607601</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>186.2473569726624</v>
+        <v>79.28987158578938</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>141.9459918185251</v>
+        <v>44.14428552145782</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20624310447914</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.854684374605644</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1290613230477</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.83651992143135</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.509969026860599</v>
+        <v>0.6980226177194822</v>
       </c>
       <c r="C2" t="n">
-        <v>17.92474958413826</v>
+        <v>3.134720419660066</v>
       </c>
       <c r="D2" t="n">
-        <v>15.45958109877452</v>
+        <v>14.66043846751762</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.92671307954676</v>
+        <v>5.934664872171969</v>
       </c>
       <c r="C3" t="n">
-        <v>35.5343581552133</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="D3" t="n">
-        <v>55.93998418798326</v>
+        <v>58.20291264627215</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.07722357793278</v>
+        <v>17.93162181806799</v>
       </c>
       <c r="C4" t="n">
-        <v>84.336054785618</v>
+        <v>76.20620204675016</v>
       </c>
       <c r="D4" t="n">
-        <v>82.63861300497526</v>
+        <v>85.79100488331179</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.33220024359647</v>
+        <v>17.27875959474386</v>
       </c>
       <c r="C5" t="n">
-        <v>125.8600556844411</v>
+        <v>183.3904711533042</v>
       </c>
       <c r="D5" t="n">
-        <v>72.72296119208249</v>
+        <v>65.85072726235482</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.67683474551611</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>181.4947163364036</v>
+        <v>182.5010077332566</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>37.0315234041897</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.22006002113408</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6336100932547</v>
+        <v>76.23565447787756</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53802310412303</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>185.4226889010951</v>
+        <v>42.05807164993335</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>120.3671772791802</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>65.19786503903067</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.016115662009975</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2195758948859</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02014457751247</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.00829594999048</v>
+        <v>0.5232715263635499</v>
       </c>
       <c r="C2" t="n">
-        <v>12.33173291304418</v>
+        <v>4.946044933995431</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90409182462007</v>
+        <v>13.29777265402305</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.48554850744145</v>
+        <v>4.113522880794135</v>
       </c>
       <c r="C3" t="n">
-        <v>57.54023294590556</v>
+        <v>17.3425731955199</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78000036992003</v>
+        <v>56.39649687045802</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.77320058478576</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9681046851705</v>
+        <v>68.12740018850316</v>
       </c>
       <c r="D4" t="n">
-        <v>80.07330625377834</v>
+        <v>95.95013012685776</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.54431450097602</v>
+        <v>22.26112919379643</v>
       </c>
       <c r="C5" t="n">
-        <v>108.4340339340602</v>
+        <v>164.3445656909161</v>
       </c>
       <c r="D5" t="n">
-        <v>51.90990986205011</v>
+        <v>80.01243789611506</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.20382797405162</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C6" t="n">
-        <v>141.3638154299067</v>
+        <v>238.0482928395411</v>
       </c>
       <c r="D6" t="n">
-        <v>29.46421209985528</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>130.3731498808637</v>
+        <v>165.7062497567064</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>88.70581381722054</v>
+        <v>69.67954330891736</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>49.69999577979051</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.701188845010475</v>
+        <v>0.3357577148524091</v>
       </c>
       <c r="C2" t="n">
-        <v>5.432010047597601</v>
+        <v>3.634430001121692</v>
       </c>
       <c r="D2" t="n">
-        <v>8.840638076742527</v>
+        <v>9.653525175858887</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.69171552533328</v>
+        <v>3.097414006898687</v>
       </c>
       <c r="C3" t="n">
-        <v>53.87831400906496</v>
+        <v>18.57957530287089</v>
       </c>
       <c r="D3" t="n">
-        <v>58.36980975599411</v>
+        <v>54.51645001682538</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.09449412598173</v>
+        <v>12.35431311024186</v>
       </c>
       <c r="C4" t="n">
-        <v>129.6054231761427</v>
+        <v>57.82788502324987</v>
       </c>
       <c r="D4" t="n">
-        <v>89.63258365002955</v>
+        <v>101.7316423571672</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.857713002809</v>
+        <v>23.63557597974196</v>
       </c>
       <c r="C5" t="n">
-        <v>152.1463504656495</v>
+        <v>153.1526418625024</v>
       </c>
       <c r="D5" t="n">
-        <v>64.05903770210439</v>
+        <v>93.14331344041615</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>20.44784118405257</v>
       </c>
       <c r="C6" t="n">
-        <v>160.8456168729805</v>
+        <v>259.260915485202</v>
       </c>
       <c r="D6" t="n">
-        <v>35.30070220160257</v>
+        <v>57.03659637362695</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>162.9514656985898</v>
+        <v>235.8334700187603</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48228446915921</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>115.6596970373167</v>
+        <v>108.9003640935774</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>55.1359328182051</v>
+        <v>50.47655821384974</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
         <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.786600895279947</v>
+        <v>0.6371542600561799</v>
       </c>
       <c r="C2" t="n">
-        <v>6.054438092090079</v>
+        <v>4.498367980858886</v>
       </c>
       <c r="D2" t="n">
-        <v>10.56164180228719</v>
+        <v>12.15403657857551</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.12167996206437</v>
+        <v>2.12057504117311</v>
       </c>
       <c r="C3" t="n">
-        <v>36.42283982755666</v>
+        <v>16.14974973486003</v>
       </c>
       <c r="D3" t="n">
-        <v>52.51859343868312</v>
+        <v>50.00041057729005</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>9.227446672215772</v>
       </c>
       <c r="C4" t="n">
-        <v>133.2810865808427</v>
+        <v>51.95703375185395</v>
       </c>
       <c r="D4" t="n">
-        <v>97.03496134005049</v>
+        <v>105.1648140789183</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>21.86843011209771</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6988220478957</v>
+        <v>131.7014545247096</v>
       </c>
       <c r="D5" t="n">
-        <v>78.7361658805942</v>
+        <v>106.0532957512617</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.46800022195202</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="C6" t="n">
-        <v>200.0104780384985</v>
+        <v>253.18291544821</v>
       </c>
       <c r="D6" t="n">
-        <v>44.84034464376883</v>
+        <v>70.03788122096746</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>195.0506886366435</v>
+        <v>302.6669267330661</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>45.39405034896402</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>161.4729536559941</v>
+        <v>198.1903177948248</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>92.85467961536754</v>
+        <v>85.97655519941439</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.264891953697392</v>
+        <v>0.4280419990516093</v>
       </c>
       <c r="C2" t="n">
-        <v>2.913827186204533</v>
+        <v>2.338523031515902</v>
       </c>
       <c r="D2" t="n">
-        <v>7.385687979048754</v>
+        <v>8.750317287951821</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.93023915973625</v>
+        <v>3.180862561759666</v>
       </c>
       <c r="C3" t="n">
-        <v>33.35487825178538</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="D3" t="n">
-        <v>51.36994862471436</v>
+        <v>54.32010047597602</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.06668639509333</v>
+        <v>15.00895890252524</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0731359939917</v>
+        <v>73.81957337772617</v>
       </c>
       <c r="D4" t="n">
-        <v>102.5484564471006</v>
+        <v>109.3254608495163</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.34353924769093</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C5" t="n">
-        <v>235.4721868635975</v>
+        <v>205.5043381914636</v>
       </c>
       <c r="D5" t="n">
-        <v>83.12948685709868</v>
+        <v>98.4692947359551</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.98748362621883</v>
+        <v>9.137125883425066</v>
       </c>
       <c r="C6" t="n">
-        <v>241.8722001475825</v>
+        <v>263.8496042548516</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>61.102013616913</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>207.5071035081271</v>
+        <v>139.356141374722</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>115.9100427018997</v>
+        <v>63.33745313948297</v>
       </c>
       <c r="D8" t="n">
         <v>31.2097595180061</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.038509144643878</v>
+        <v>0.2081305133003238</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14185469549705</v>
+        <v>2.170644174089698</v>
       </c>
       <c r="D2" t="n">
-        <v>7.153995520846507</v>
+        <v>6.495242811296897</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.41910845872215</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C3" t="n">
-        <v>22.04023596034089</v>
+        <v>13.56284453416968</v>
       </c>
       <c r="D3" t="n">
-        <v>46.4464838879166</v>
+        <v>48.90085314853363</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.25888796094745</v>
+        <v>9.967684441217866</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7383757223767</v>
+        <v>58.21076662790613</v>
       </c>
       <c r="D4" t="n">
-        <v>104.1820846269673</v>
+        <v>106.8750185797163</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.46750150033328</v>
+        <v>15.21708941582556</v>
       </c>
       <c r="C5" t="n">
-        <v>240.160032151376</v>
+        <v>155.5088363526948</v>
       </c>
       <c r="D5" t="n">
-        <v>97.02121687219106</v>
+        <v>102.34719816773</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>9.177377539299185</v>
       </c>
       <c r="C6" t="n">
-        <v>301.6056574647754</v>
+        <v>243.6835246619178</v>
       </c>
       <c r="D6" t="n">
-        <v>56.31206656789281</v>
+        <v>64.32214608684252</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>271.166569894603</v>
+        <v>181.8756344456513</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>179.2474958413826</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>73.21874378272709</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.972331137831842</v>
+        <v>0.2866703296400686</v>
       </c>
       <c r="C2" t="n">
-        <v>5.550801519811467</v>
+        <v>5.447718010865551</v>
       </c>
       <c r="D2" t="n">
-        <v>5.69708192774424</v>
+        <v>7.831401436776806</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.64352777236717</v>
+        <v>1.438260386721577</v>
       </c>
       <c r="C3" t="n">
-        <v>32.088423713307</v>
+        <v>10.54397034361075</v>
       </c>
       <c r="D3" t="n">
-        <v>43.08399800087128</v>
+        <v>42.75020378142736</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.07271575003904</v>
+        <v>7.057784245830319</v>
       </c>
       <c r="C4" t="n">
-        <v>88.31802347404307</v>
+        <v>43.99309637500382</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0799828657256</v>
+        <v>107.5131545874767</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.66447293598841</v>
+        <v>15.51161372709961</v>
       </c>
       <c r="C5" t="n">
-        <v>233.3368856068607</v>
+        <v>129.9097649644592</v>
       </c>
       <c r="D5" t="n">
-        <v>105.9060335956247</v>
+        <v>118.055161435679</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.52462279362885</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>341.8170616830205</v>
+        <v>246.8231538200991</v>
       </c>
       <c r="D6" t="n">
-        <v>66.17372225705202</v>
+        <v>81.30834486572085</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>331.4124995134127</v>
+        <v>275.6580656415322</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>226.8131721121406</v>
+        <v>160.7219166622453</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>83.09218044433726</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.816634163484099</v>
+        <v>0.1492256510455152</v>
       </c>
       <c r="C2" t="n">
-        <v>5.106069809787661</v>
+        <v>9.224501429103031</v>
       </c>
       <c r="D2" t="n">
-        <v>10.30736914688726</v>
+        <v>16.73192612347839</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.287333282174826</v>
+        <v>1.187914722138641</v>
       </c>
       <c r="C3" t="n">
-        <v>27.10605411425443</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="D3" t="n">
-        <v>38.98520133564084</v>
+        <v>39.60370238931633</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.32498385230147</v>
+        <v>4.849833658979244</v>
       </c>
       <c r="C4" t="n">
-        <v>84.45091926701488</v>
+        <v>34.05093737409637</v>
       </c>
       <c r="D4" t="n">
-        <v>100.9786418680099</v>
+        <v>103.8374911827766</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.75635630956011</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C5" t="n">
-        <v>203.4917553977577</v>
+        <v>104.1388877279804</v>
       </c>
       <c r="D5" t="n">
-        <v>115.3308115563941</v>
+        <v>129.7870465014284</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.17872880656449</v>
+        <v>18.15349679922777</v>
       </c>
       <c r="C6" t="n">
-        <v>354.2950750039975</v>
+        <v>227.6633656240184</v>
       </c>
       <c r="D6" t="n">
-        <v>78.73223888977722</v>
+        <v>98.49580192396976</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.18852092141116</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>395.4911721696021</v>
+        <v>319.4950641315607</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>55.69454726192155</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>309.5106899793706</v>
+        <v>263.5305362509713</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>152.3171745661883</v>
+        <v>128.7984265632518</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.635812659453438</v>
+        <v>2.698824438974482</v>
       </c>
       <c r="C2" t="n">
-        <v>9.196030745679874</v>
+        <v>10.16501572977148</v>
       </c>
       <c r="D2" t="n">
-        <v>6.475607857211961</v>
+        <v>9.524916226602555</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.036144738607885</v>
+        <v>0.2366011967234813</v>
       </c>
       <c r="C2" t="n">
-        <v>2.98254952550181</v>
+        <v>8.009097771245479</v>
       </c>
       <c r="D2" t="n">
-        <v>7.668431317871836</v>
+        <v>17.28366833326509</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.5271007061893</v>
+        <v>0.8393942871310229</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1922679857789</v>
+        <v>26.59554530804609</v>
       </c>
       <c r="D3" t="n">
-        <v>42.91710089114932</v>
+        <v>42.93182710671302</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.09671966329748</v>
+        <v>3.548036203147973</v>
       </c>
       <c r="C4" t="n">
-        <v>121.6925366799134</v>
+        <v>37.34371917414018</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5394407913131</v>
+        <v>100.5319466625776</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.44047022850411</v>
+        <v>10.77468105410875</v>
       </c>
       <c r="C5" t="n">
-        <v>300.414797499524</v>
+        <v>84.13577825395166</v>
       </c>
       <c r="D5" t="n">
-        <v>107.0104997629024</v>
+        <v>135.3093773378167</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.86544381125596</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>326.440929139107</v>
+        <v>200.3324912854914</v>
       </c>
       <c r="D6" t="n">
-        <v>65.04667589257669</v>
+        <v>114.7172192412398</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>217.6279405912074</v>
+        <v>324.4656527581623</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>68.45039518320036</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>112.2383062880166</v>
+        <v>339.969412503628</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>217.6593565177433</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>93.3838416279566</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.343071917138642</v>
+        <v>3.042436135460865</v>
       </c>
       <c r="C2" t="n">
-        <v>9.610328276872027</v>
+        <v>6.776022654711485</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23748513343649</v>
+        <v>14.31780851873548</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.851838212116743</v>
+        <v>4.471860792844221</v>
       </c>
       <c r="C3" t="n">
-        <v>23.16924582022473</v>
+        <v>20.06692307480481</v>
       </c>
       <c r="D3" t="n">
-        <v>8.575566196595888</v>
+        <v>9.53277020823653</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39851595038474</v>
+        <v>11.67815149728358</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14517174024955</v>
+        <v>59.94784435272239</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576295994162911</v>
+        <v>0.7785434331522388</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.62599518241097</v>
+        <v>2.478912953223196</v>
       </c>
       <c r="C2" t="n">
-        <v>8.93881284716721</v>
+        <v>8.532369297609028</v>
       </c>
       <c r="D2" t="n">
-        <v>15.53517567200153</v>
+        <v>16.25479673921444</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.04804888424586</v>
+        <v>8.320311793491717</v>
       </c>
       <c r="C3" t="n">
-        <v>32.12278488295564</v>
+        <v>24.35716054236337</v>
       </c>
       <c r="D3" t="n">
-        <v>16.78297700409922</v>
+        <v>19.73312885536089</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.56302446061893</v>
+        <v>5.717698629533424</v>
       </c>
       <c r="C4" t="n">
-        <v>35.83771819582557</v>
+        <v>33.15754696323177</v>
       </c>
       <c r="D4" t="n">
-        <v>19.56524999793468</v>
+        <v>19.22065655374405</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44151358579321</v>
+        <v>13.63037023192137</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14739158389898</v>
+        <v>73.76435654922152</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25084496543015</v>
+        <v>1.603572968461338</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.51211244871834</v>
+        <v>2.669372007847077</v>
       </c>
       <c r="C2" t="n">
-        <v>5.64504929941916</v>
+        <v>4.014366362665207</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35042717715388</v>
+        <v>17.94143929511046</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>8.555931242510953</v>
       </c>
       <c r="C3" t="n">
-        <v>33.73775985644163</v>
+        <v>30.14947199741955</v>
       </c>
       <c r="D3" t="n">
-        <v>25.314364554004</v>
+        <v>28.61794557879453</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.72589676853267</v>
+        <v>12.00971966605123</v>
       </c>
       <c r="C4" t="n">
-        <v>62.09063355508952</v>
+        <v>50.70628717664351</v>
       </c>
       <c r="D4" t="n">
-        <v>23.58550684682537</v>
+        <v>25.10427054529519</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.40652566501619</v>
+        <v>5.816855147662352</v>
       </c>
       <c r="C5" t="n">
-        <v>40.0307626406637</v>
+        <v>39.31899555508476</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>26.67899386290708</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73368405342321</v>
+        <v>14.843072060086</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0754727258816</v>
+        <v>87.40920213161755</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183421013355803</v>
+        <v>2.473845343347667</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.982369599052562</v>
+        <v>2.238384765682728</v>
       </c>
       <c r="C2" t="n">
-        <v>8.646252031301659</v>
+        <v>9.220574438286043</v>
       </c>
       <c r="D2" t="n">
-        <v>14.62116855934775</v>
+        <v>22.18160762975243</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06139244147782</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C3" t="n">
-        <v>26.89497835784137</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D3" t="n">
-        <v>32.86891313818321</v>
+        <v>36.32957379565322</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.89930625928586</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="C4" t="n">
-        <v>74.57257386688347</v>
+        <v>65.58761887761666</v>
       </c>
       <c r="D4" t="n">
-        <v>30.56671477172444</v>
+        <v>33.56595400819845</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.87472150895069</v>
+        <v>12.27184630308513</v>
       </c>
       <c r="C5" t="n">
-        <v>80.33150589999526</v>
+        <v>70.88218424661972</v>
       </c>
       <c r="D5" t="n">
-        <v>31.02322745419922</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.10316562440393</v>
+        <v>6.400013283984958</v>
       </c>
       <c r="C6" t="n">
-        <v>38.64158963915446</v>
+        <v>39.32586778901449</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05644347296937</v>
+        <v>16.08917850180998</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7967978950859</v>
+        <v>101.6158642219578</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018814490989792</v>
+        <v>3.387195474065258</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.339725763398402</v>
+        <v>1.91440802328128</v>
       </c>
       <c r="C2" t="n">
-        <v>7.792131528606935</v>
+        <v>7.848091147749003</v>
       </c>
       <c r="D2" t="n">
-        <v>23.43628119577986</v>
+        <v>18.97521962768235</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.79984664152067</v>
+        <v>8.261406931236911</v>
       </c>
       <c r="C3" t="n">
-        <v>28.86829124337746</v>
+        <v>29.77640786980576</v>
       </c>
       <c r="D3" t="n">
-        <v>34.49861432723292</v>
+        <v>45.1063982716197</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.63281066307847</v>
+        <v>16.15760371649401</v>
       </c>
       <c r="C4" t="n">
-        <v>58.97652983721864</v>
+        <v>58.50430919147592</v>
       </c>
       <c r="D4" t="n">
-        <v>34.58697162061513</v>
+        <v>43.32943492693298</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.70858516275472</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C5" t="n">
-        <v>82.56498192715677</v>
+        <v>98.56746950637979</v>
       </c>
       <c r="D5" t="n">
-        <v>28.00435326364027</v>
+        <v>35.36746104549135</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>11.59247689174634</v>
       </c>
       <c r="C6" t="n">
-        <v>56.714583126634</v>
+        <v>78.00770908404307</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>24.852943133008</v>
+        <v>37.96811071404115</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055580367331901</v>
+        <v>17.3614699668057</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14606594373657</v>
+        <v>115.4537752792579</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409737729582438</v>
+        <v>4.340367491701424</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.44182752464007</v>
+        <v>2.195187866695868</v>
       </c>
       <c r="C2" t="n">
-        <v>5.972953032637593</v>
+        <v>6.683738370512286</v>
       </c>
       <c r="D2" t="n">
-        <v>17.37202562664731</v>
+        <v>20.06790482250905</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.37202562664731</v>
+        <v>7.382742735936015</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88930885579414</v>
+        <v>30.0709321810798</v>
       </c>
       <c r="D3" t="n">
-        <v>45.84761778832605</v>
+        <v>49.16592502868026</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.07423727709104</v>
+        <v>15.88958659323463</v>
       </c>
       <c r="C4" t="n">
-        <v>67.46373874043232</v>
+        <v>66.34061936677396</v>
       </c>
       <c r="D4" t="n">
-        <v>44.31216437888403</v>
+        <v>54.36918786118836</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.34167356327368</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="C5" t="n">
-        <v>98.91108120286617</v>
+        <v>103.4762080276138</v>
       </c>
       <c r="D5" t="n">
-        <v>34.90113088597411</v>
+        <v>42.55876297909924</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.96482131356314</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>100.588888029424</v>
+        <v>117.3335768730576</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>58.09001166028376</v>
+        <v>74.67860261894212</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.21805546799658</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276369584524546</v>
+        <v>18.654473895022</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49233443944217</v>
+        <v>128.8047007037233</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45727718839341</v>
+        <v>5.329849684291999</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.350124077517616</v>
+        <v>1.98214861487431</v>
       </c>
       <c r="C2" t="n">
-        <v>9.077239273466008</v>
+        <v>4.116468123906875</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31213901668826</v>
+        <v>15.76097764397829</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.21141991377833</v>
+        <v>10.36234701832508</v>
       </c>
       <c r="C3" t="n">
-        <v>26.14394136409256</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="D3" t="n">
-        <v>49.10702016642546</v>
+        <v>54.48208884717674</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>10.03149804199391</v>
       </c>
       <c r="C4" t="n">
-        <v>71.11387670482196</v>
+        <v>93.67836593923064</v>
       </c>
       <c r="D4" t="n">
-        <v>57.34290165735195</v>
+        <v>51.71454206890498</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.69848994827177</v>
+        <v>9.719302272043425</v>
       </c>
       <c r="C5" t="n">
-        <v>113.7109278443868</v>
+        <v>70.09678608322227</v>
       </c>
       <c r="D5" t="n">
-        <v>42.68148144213009</v>
+        <v>36.00559705325178</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.38370878810704</v>
+        <v>6.480516595733197</v>
       </c>
       <c r="C6" t="n">
-        <v>131.9449279553629</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="D6" t="n">
-        <v>37.0315234041897</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>105.0411138681832</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>54.40845776935822</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.484269812717949</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.19803539307694</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.548736086128206</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
